--- a/ws-subprg/ws_subprgList_appCore.xlsx
+++ b/ws-subprg/ws_subprgList_appCore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\ws-subprg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF32F26-9C09-44B6-8636-EA41CEB81C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFCDE1C-832F-41DE-BB8D-F66730C91082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sottoprogramma" sheetId="3" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="267">
   <si>
     <t>Nome</t>
   </si>
@@ -680,9 +680,6 @@
     <t>YCLEAN_SOH</t>
   </si>
   <si>
-    <t>tunnel *</t>
-  </si>
-  <si>
     <t>AS_BCGBPC</t>
   </si>
   <si>
@@ -695,9 +692,6 @@
     <t>aggiorna/controlla</t>
   </si>
   <si>
-    <t>pulisci</t>
-  </si>
-  <si>
     <t>YSTCKINV</t>
   </si>
   <si>
@@ -795,6 +789,48 @@
   </si>
   <si>
     <t>YDEM_USR</t>
+  </si>
+  <si>
+    <t>YOBPCSOH</t>
+  </si>
+  <si>
+    <t>C_GIACYITM</t>
+  </si>
+  <si>
+    <t>C_FCYINV</t>
+  </si>
+  <si>
+    <t>YCLN_CSTK</t>
+  </si>
+  <si>
+    <t>C_YLOCINV</t>
+  </si>
+  <si>
+    <t>YCLEAN_INV</t>
+  </si>
+  <si>
+    <t>YCREA_INV</t>
+  </si>
+  <si>
+    <t>C_FCYVXP</t>
+  </si>
+  <si>
+    <t>C_LOCDVXP</t>
+  </si>
+  <si>
+    <t>C_PRHVXP</t>
+  </si>
+  <si>
+    <t>C_PRLVXP</t>
+  </si>
+  <si>
+    <t>C_QTYVXP</t>
+  </si>
+  <si>
+    <t>C_SRTNMVXP</t>
+  </si>
+  <si>
+    <t>YOKVXP</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1416,6 +1452,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1696,17 +1735,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C11CF176-524D-4F01-A4B5-47E90085D90F}">
-  <dimension ref="A1:I125"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I134"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
-    <col min="8" max="9" width="22.6640625" customWidth="1"/>
+    <col min="1" max="1" width="28.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="3" max="3" width="44.140625" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="8" max="9" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>15</v>
       </c>
@@ -1732,9 +1771,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B2" s="26" t="s">
         <v>24</v>
@@ -1758,9 +1797,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>26</v>
@@ -1784,7 +1823,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="28"/>
       <c r="B4" s="14" t="s">
         <v>28</v>
@@ -1808,7 +1847,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="28"/>
       <c r="B5" s="14" t="s">
         <v>30</v>
@@ -1832,7 +1871,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="28"/>
       <c r="B6" s="14" t="s">
         <v>32</v>
@@ -1856,7 +1895,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="28"/>
       <c r="B7" s="14" t="s">
         <v>34</v>
@@ -1880,7 +1919,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="28"/>
       <c r="B8" s="14" t="s">
         <v>212</v>
@@ -1902,7 +1941,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="31"/>
       <c r="B9" s="32" t="s">
         <v>36</v>
@@ -1926,7 +1965,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -1935,9 +1974,9 @@
       <c r="G10" s="5"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B11" s="26" t="s">
         <v>60</v>
@@ -1961,9 +2000,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>61</v>
@@ -1987,7 +2026,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="28"/>
       <c r="B13" s="14" t="s">
         <v>62</v>
@@ -2011,7 +2050,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="28"/>
       <c r="B14" s="14" t="s">
         <v>63</v>
@@ -2035,7 +2074,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="28"/>
       <c r="B15" s="14" t="s">
         <v>64</v>
@@ -2059,7 +2098,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="28"/>
       <c r="B16" s="14" t="s">
         <v>65</v>
@@ -2083,7 +2122,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
       <c r="B17" s="14" t="s">
         <v>213</v>
@@ -2105,7 +2144,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="31"/>
       <c r="B18" s="32" t="s">
         <v>66</v>
@@ -2129,7 +2168,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -2138,9 +2177,9 @@
       <c r="G19" s="5"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="24" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B20" s="26" t="s">
         <v>75</v>
@@ -2164,9 +2203,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>76</v>
@@ -2190,7 +2229,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="28"/>
       <c r="B22" s="14" t="s">
         <v>77</v>
@@ -2214,7 +2253,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="28"/>
       <c r="B23" s="14" t="s">
         <v>78</v>
@@ -2238,7 +2277,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="28"/>
       <c r="B24" s="14" t="s">
         <v>79</v>
@@ -2262,7 +2301,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="28"/>
       <c r="B25" s="14" t="s">
         <v>80</v>
@@ -2286,7 +2325,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="28"/>
       <c r="B26" s="14" t="s">
         <v>81</v>
@@ -2310,7 +2349,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="28"/>
       <c r="B27" s="14" t="s">
         <v>82</v>
@@ -2334,7 +2373,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="28"/>
       <c r="B28" s="14" t="s">
         <v>83</v>
@@ -2358,7 +2397,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="28"/>
       <c r="B29" s="14" t="s">
         <v>84</v>
@@ -2382,7 +2421,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="28"/>
       <c r="B30" s="14" t="s">
         <v>215</v>
@@ -2404,10 +2443,10 @@
         <v>215</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="28"/>
-      <c r="B31" s="35" t="s">
-        <v>216</v>
+      <c r="B31" s="72" t="s">
+        <v>253</v>
       </c>
       <c r="C31" s="30"/>
       <c r="D31" s="5" t="s">
@@ -2422,9 +2461,11 @@
       <c r="G31" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H31" s="36"/>
-    </row>
-    <row r="32" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H31" s="72" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="31"/>
       <c r="B32" s="32" t="s">
         <v>85</v>
@@ -2448,7 +2489,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -2457,9 +2498,9 @@
       <c r="G33" s="5"/>
       <c r="H33" s="16"/>
     </row>
-    <row r="34" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="24" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B34" s="26" t="s">
         <v>86</v>
@@ -2483,12 +2524,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="28" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>87</v>
+        <v>254</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>149</v>
@@ -2509,7 +2550,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="28"/>
       <c r="B36" s="14" t="s">
         <v>88</v>
@@ -2533,7 +2574,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="28"/>
       <c r="B37" s="14" t="s">
         <v>89</v>
@@ -2557,7 +2598,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="31"/>
       <c r="B38" s="32" t="s">
         <v>152</v>
@@ -2581,7 +2622,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2591,9 +2632,9 @@
       <c r="G39" s="5"/>
       <c r="H39" s="16"/>
     </row>
-    <row r="40" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="37" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B40" s="26" t="s">
         <v>90</v>
@@ -2617,12 +2658,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="38" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C41" s="30"/>
       <c r="D41" s="5" t="s">
@@ -2638,10 +2679,10 @@
         <v>23</v>
       </c>
       <c r="H41" s="29" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="38"/>
       <c r="B42" s="5" t="s">
         <v>154</v>
@@ -2665,7 +2706,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="38"/>
       <c r="B43" s="5" t="s">
         <v>157</v>
@@ -2689,7 +2730,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="38"/>
       <c r="B44" s="5" t="s">
         <v>162</v>
@@ -2713,7 +2754,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="38"/>
       <c r="B45" s="5" t="s">
         <v>165</v>
@@ -2737,7 +2778,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="38"/>
       <c r="B46" s="5" t="s">
         <v>167</v>
@@ -2761,7 +2802,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="38"/>
       <c r="B47" s="5" t="s">
         <v>169</v>
@@ -2785,7 +2826,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="38"/>
       <c r="B48" s="5" t="s">
         <v>171</v>
@@ -2809,7 +2850,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="38"/>
       <c r="B49" s="5" t="s">
         <v>91</v>
@@ -2833,7 +2874,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="38"/>
       <c r="B50" s="5" t="s">
         <v>92</v>
@@ -2857,7 +2898,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="38"/>
       <c r="B51" s="5" t="s">
         <v>93</v>
@@ -2881,7 +2922,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="38"/>
       <c r="B52" s="5" t="s">
         <v>94</v>
@@ -2905,10 +2946,10 @@
         <v>94</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="38"/>
       <c r="B53" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C53" s="30"/>
       <c r="D53" s="5" t="s">
@@ -2924,10 +2965,10 @@
         <v>23</v>
       </c>
       <c r="H53" s="29" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="39"/>
       <c r="B54" s="33" t="s">
         <v>95</v>
@@ -2951,7 +2992,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
@@ -2960,7 +3001,7 @@
       <c r="G55" s="5"/>
       <c r="H55" s="6"/>
     </row>
-    <row r="56" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="25" t="s">
         <v>174</v>
       </c>
@@ -2986,7 +3027,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="28"/>
       <c r="B57" s="14" t="s">
         <v>97</v>
@@ -3010,7 +3051,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="28"/>
       <c r="B58" s="14" t="s">
         <v>98</v>
@@ -3034,7 +3075,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="28"/>
       <c r="B59" s="14" t="s">
         <v>99</v>
@@ -3058,7 +3099,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="28"/>
       <c r="B60" s="14" t="s">
         <v>100</v>
@@ -3082,7 +3123,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="28"/>
       <c r="B61" s="14" t="s">
         <v>101</v>
@@ -3106,7 +3147,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="28"/>
       <c r="B62" s="14" t="s">
         <v>181</v>
@@ -3130,7 +3171,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="28"/>
       <c r="B63" s="14" t="s">
         <v>185</v>
@@ -3154,7 +3195,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="28"/>
       <c r="B64" s="14" t="s">
         <v>102</v>
@@ -3178,7 +3219,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="31"/>
       <c r="B65" s="32" t="s">
         <v>103</v>
@@ -3202,7 +3243,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="14"/>
       <c r="D66" s="5"/>
       <c r="E66" s="5"/>
@@ -3210,9 +3251,9 @@
       <c r="G66" s="6"/>
       <c r="H66" s="6"/>
     </row>
-    <row r="67" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="25" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B67" s="40" t="s">
         <v>186</v>
@@ -3236,9 +3277,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="28" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>188</v>
@@ -3262,7 +3303,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="28"/>
       <c r="B69" s="14" t="s">
         <v>190</v>
@@ -3286,7 +3327,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="28"/>
       <c r="B70" s="14" t="s">
         <v>200</v>
@@ -3310,7 +3351,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="28"/>
       <c r="B71" s="14" t="s">
         <v>201</v>
@@ -3334,7 +3375,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="31"/>
       <c r="B72" s="32" t="s">
         <v>203</v>
@@ -3358,7 +3399,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B73" s="14"/>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
@@ -3367,9 +3408,9 @@
       <c r="G73" s="6"/>
       <c r="H73" s="6"/>
     </row>
-    <row r="74" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="25" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B74" s="56" t="s">
         <v>104</v>
@@ -3393,9 +3434,9 @@
         <v>104</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="28" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B75" s="48" t="s">
         <v>105</v>
@@ -3419,7 +3460,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="28"/>
       <c r="B76" s="48" t="s">
         <v>106</v>
@@ -3443,10 +3484,10 @@
         <v>106</v>
       </c>
       <c r="I76" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="28"/>
       <c r="B77" s="14" t="s">
         <v>208</v>
@@ -3470,7 +3511,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="28"/>
       <c r="B78" s="14" t="s">
         <v>107</v>
@@ -3494,7 +3535,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="31"/>
       <c r="B79" s="32" t="s">
         <v>108</v>
@@ -3518,7 +3559,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
@@ -3527,9 +3568,9 @@
       <c r="G80" s="5"/>
       <c r="H80" s="6"/>
     </row>
-    <row r="81" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="24" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B81" s="26" t="s">
         <v>109</v>
@@ -3551,9 +3592,9 @@
         <v>109</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="28" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B82" s="14" t="s">
         <v>110</v>
@@ -3575,7 +3616,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="28"/>
       <c r="B83" s="14" t="s">
         <v>111</v>
@@ -3597,7 +3638,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="28"/>
       <c r="B84" s="14" t="s">
         <v>112</v>
@@ -3619,7 +3660,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="28"/>
       <c r="B85" s="14" t="s">
         <v>113</v>
@@ -3641,7 +3682,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="28"/>
       <c r="B86" s="14" t="s">
         <v>114</v>
@@ -3663,7 +3704,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="28"/>
       <c r="B87" s="14" t="s">
         <v>115</v>
@@ -3685,7 +3726,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="28"/>
       <c r="B88" s="14" t="s">
         <v>116</v>
@@ -3707,10 +3748,10 @@
         <v>116</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="28"/>
       <c r="B89" s="35" t="s">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="C89" s="52"/>
       <c r="D89" s="5" t="s">
@@ -3725,9 +3766,11 @@
       <c r="G89" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H89" s="36"/>
-    </row>
-    <row r="90" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H89" s="36" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="31"/>
       <c r="B90" s="32" t="s">
         <v>117</v>
@@ -3749,7 +3792,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B91" s="5"/>
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
@@ -3757,46 +3800,56 @@
       <c r="G91" s="5"/>
       <c r="H91" s="14"/>
     </row>
-    <row r="92" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="B92" s="61"/>
+        <v>220</v>
+      </c>
+      <c r="B92" s="61" t="s">
+        <v>255</v>
+      </c>
       <c r="C92" s="41"/>
       <c r="D92" s="26"/>
       <c r="E92" s="26"/>
       <c r="F92" s="26"/>
       <c r="G92" s="26"/>
-      <c r="H92" s="27"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H92" s="27" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="28"/>
-      <c r="B93" s="62"/>
+      <c r="B93" s="62" t="s">
+        <v>257</v>
+      </c>
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
       <c r="H93" s="29"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="28"/>
-      <c r="B94" s="62"/>
+      <c r="B94" s="62" t="s">
+        <v>258</v>
+      </c>
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
       <c r="G94" s="5"/>
       <c r="H94" s="29"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="28"/>
-      <c r="B95" s="62"/>
+      <c r="B95" s="62" t="s">
+        <v>259</v>
+      </c>
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
       <c r="G95" s="5"/>
       <c r="H95" s="29"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="28"/>
       <c r="B96" s="62"/>
       <c r="D96" s="5"/>
@@ -3805,7 +3858,7 @@
       <c r="G96" s="5"/>
       <c r="H96" s="29"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="28"/>
       <c r="B97" s="62"/>
       <c r="D97" s="5"/>
@@ -3814,7 +3867,7 @@
       <c r="G97" s="5"/>
       <c r="H97" s="29"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="28"/>
       <c r="B98" s="62"/>
       <c r="D98" s="5"/>
@@ -3823,7 +3876,7 @@
       <c r="G98" s="5"/>
       <c r="H98" s="29"/>
     </row>
-    <row r="99" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="31"/>
       <c r="B99" s="63"/>
       <c r="C99" s="45"/>
@@ -3833,7 +3886,7 @@
       <c r="G99" s="33"/>
       <c r="H99" s="34"/>
     </row>
-    <row r="100" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B100" s="5"/>
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
@@ -3841,7 +3894,7 @@
       <c r="G100" s="5"/>
       <c r="H100" s="16"/>
     </row>
-    <row r="101" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="24" t="s">
         <v>118</v>
       </c>
@@ -3865,7 +3918,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="28" t="s">
         <v>214</v>
       </c>
@@ -3889,9 +3942,9 @@
         <v>120</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="55" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B103" s="14" t="s">
         <v>121</v>
@@ -3913,7 +3966,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="28"/>
       <c r="B104" s="14" t="s">
         <v>122</v>
@@ -3935,7 +3988,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="28"/>
       <c r="B105" s="14" t="s">
         <v>122</v>
@@ -3957,7 +4010,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="28"/>
       <c r="B106" s="14" t="s">
         <v>123</v>
@@ -3979,7 +4032,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="28"/>
       <c r="B107" s="14" t="s">
         <v>124</v>
@@ -4001,7 +4054,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="28"/>
       <c r="B108" s="14" t="s">
         <v>125</v>
@@ -4023,7 +4076,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="28"/>
       <c r="B109" s="14" t="s">
         <v>126</v>
@@ -4045,7 +4098,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="28"/>
       <c r="B110" s="14" t="s">
         <v>127</v>
@@ -4067,7 +4120,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="28"/>
       <c r="B111" s="14" t="s">
         <v>128</v>
@@ -4089,7 +4142,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="28"/>
       <c r="B112" s="14" t="s">
         <v>129</v>
@@ -4111,7 +4164,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="28"/>
       <c r="B113" s="14" t="s">
         <v>130</v>
@@ -4133,7 +4186,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="28"/>
       <c r="B114" s="14" t="s">
         <v>131</v>
@@ -4155,7 +4208,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="28"/>
       <c r="B115" s="14" t="s">
         <v>132</v>
@@ -4177,7 +4230,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="28"/>
       <c r="B116" s="14" t="s">
         <v>133</v>
@@ -4199,7 +4252,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="28"/>
       <c r="B117" s="14" t="s">
         <v>134</v>
@@ -4221,7 +4274,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="31"/>
       <c r="B118" s="32" t="s">
         <v>135</v>
@@ -4243,17 +4296,17 @@
         <v>135</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="120" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="120" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="B120" s="60" t="s">
+        <v>222</v>
+      </c>
+      <c r="C120" s="41" t="s">
         <v>223</v>
       </c>
-      <c r="B120" s="60" t="s">
-        <v>224</v>
-      </c>
-      <c r="C120" s="41" t="s">
-        <v>225</v>
-      </c>
       <c r="D120" s="26" t="s">
         <v>136</v>
       </c>
@@ -4267,16 +4320,16 @@
         <v>23</v>
       </c>
       <c r="H120" s="43" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="66"/>
       <c r="B121" s="28"/>
       <c r="G121" s="68"/>
       <c r="H121" s="64"/>
     </row>
-    <row r="122" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="67"/>
       <c r="B122" s="31"/>
       <c r="C122" s="45"/>
@@ -4286,17 +4339,17 @@
       <c r="G122" s="69"/>
       <c r="H122" s="65"/>
     </row>
-    <row r="123" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="124" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="124" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="24" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B124" s="60" t="s">
+        <v>233</v>
+      </c>
+      <c r="C124" s="41" t="s">
         <v>235</v>
       </c>
-      <c r="C124" s="41" t="s">
-        <v>237</v>
-      </c>
       <c r="D124" s="26" t="s">
         <v>136</v>
       </c>
@@ -4310,10 +4363,10 @@
         <v>23</v>
       </c>
       <c r="H124" s="71" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="67"/>
       <c r="B125" s="31"/>
       <c r="C125" s="45"/>
@@ -4322,6 +4375,41 @@
       <c r="F125" s="45"/>
       <c r="G125" s="69"/>
       <c r="H125" s="65"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B133" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B134" t="s">
+        <v>266</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4332,16 +4420,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A8BD388-3A0C-4C89-946B-F584CA19B428}">
   <dimension ref="A1:F48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
-    <col min="6" max="6" width="37.109375" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="37.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>38</v>
       </c>
@@ -4361,7 +4449,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>24</v>
       </c>
@@ -4381,7 +4469,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>26</v>
       </c>
@@ -4401,7 +4489,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>28</v>
       </c>
@@ -4421,7 +4509,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>30</v>
       </c>
@@ -4441,7 +4529,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>32</v>
       </c>
@@ -4461,7 +4549,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>34</v>
       </c>
@@ -4481,7 +4569,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>36</v>
       </c>
@@ -4501,7 +4589,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>212</v>
       </c>
@@ -4521,7 +4609,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="14" t="s">
         <v>49</v>
@@ -4539,7 +4627,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="14" t="s">
         <v>50</v>
@@ -4557,7 +4645,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="14" t="s">
         <v>51</v>
@@ -4575,7 +4663,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="14" t="s">
         <v>52</v>
@@ -4593,7 +4681,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
       <c r="B15" s="17" t="s">
         <v>53</v>
@@ -4611,7 +4699,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>60</v>
       </c>
@@ -4631,7 +4719,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>61</v>
       </c>
@@ -4651,7 +4739,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>62</v>
       </c>
@@ -4671,7 +4759,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>63</v>
       </c>
@@ -4691,7 +4779,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>64</v>
       </c>
@@ -4711,7 +4799,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>65</v>
       </c>
@@ -4731,7 +4819,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>66</v>
       </c>
@@ -4751,7 +4839,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>213</v>
       </c>
@@ -4771,7 +4859,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="18"/>
       <c r="B24" s="14" t="s">
         <v>49</v>
@@ -4789,7 +4877,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="18"/>
       <c r="B25" s="14" t="s">
         <v>51</v>
@@ -4807,7 +4895,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="18"/>
       <c r="B26" s="14" t="s">
         <v>52</v>
@@ -4825,7 +4913,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="19"/>
       <c r="B27" s="17" t="s">
         <v>53</v>
@@ -4843,67 +4931,67 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="70" t="s">
+        <v>222</v>
+      </c>
+      <c r="B42" s="13" t="s">
         <v>224</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>226</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>55</v>
@@ -4915,13 +5003,13 @@
         <v>1</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="18"/>
       <c r="B43" s="14" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>55</v>
@@ -4933,13 +5021,13 @@
         <v>1</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="18"/>
       <c r="B44" s="14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>55</v>
@@ -4951,13 +5039,13 @@
         <v>1</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="18"/>
       <c r="B45" s="14" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>55</v>
@@ -4969,46 +5057,46 @@
         <v>1</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="18"/>
       <c r="B46" s="14" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>55</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E46" s="5">
         <v>1</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="18"/>
       <c r="B47" s="14" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>55</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E47" s="5">
         <v>1</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="19"/>
       <c r="B48" s="17" t="s">
         <v>10</v>
@@ -5023,7 +5111,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -5034,15 +5122,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6268CE7-055C-4EEB-B5AE-4C7D3BC4374C}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" customWidth="1"/>
-    <col min="5" max="5" width="26.88671875" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>192</v>
       </c>
@@ -5065,7 +5153,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D2" t="s">
         <v>55</v>
       </c>
@@ -5081,13 +5169,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8FE398-F589-4759-8EE8-B78ACE038FFE}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="30.33203125" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>192</v>
       </c>
@@ -5115,15 +5203,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5140,7 +5228,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -5165,13 +5253,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53235D0A-B2FF-418E-8294-1C7640EEB855}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -5182,7 +5270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -5193,7 +5281,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
